--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G458"/>
+  <dimension ref="A1:G460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12796,6 +12796,60 @@
       <c r="G458" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>303.05</v>
+      </c>
+      <c r="C459" t="n">
+        <v>306.19</v>
+      </c>
+      <c r="D459" t="n">
+        <v>308.21</v>
+      </c>
+      <c r="E459" t="n">
+        <v>299.46</v>
+      </c>
+      <c r="F459" t="n">
+        <v>289.43</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>303.38</v>
+      </c>
+      <c r="C460" t="n">
+        <v>306.52</v>
+      </c>
+      <c r="D460" t="n">
+        <v>308.41</v>
+      </c>
+      <c r="E460" t="n">
+        <v>299.19</v>
+      </c>
+      <c r="F460" t="n">
+        <v>290.37</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B593"/>
+  <dimension ref="A1:B595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18743,6 +18797,26 @@
       </c>
       <c r="B593" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -18911,28 +18985,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.425449437986427</v>
+        <v>1.420175610454164</v>
       </c>
       <c r="J2" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K2" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2347848873890717</v>
+        <v>0.2349771917738216</v>
       </c>
       <c r="M2" t="n">
-        <v>13.19187258940751</v>
+        <v>13.16608046115925</v>
       </c>
       <c r="N2" t="n">
-        <v>301.5295295009147</v>
+        <v>300.3485575859287</v>
       </c>
       <c r="O2" t="n">
-        <v>17.3646056534813</v>
+        <v>17.33056714553591</v>
       </c>
       <c r="P2" t="n">
-        <v>271.4312068052096</v>
+        <v>271.4941234568668</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18989,28 +19063,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5170476835961192</v>
+        <v>0.5143274376738004</v>
       </c>
       <c r="J3" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K3" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1234161553612172</v>
+        <v>0.1231889717236865</v>
       </c>
       <c r="M3" t="n">
-        <v>7.475080814797917</v>
+        <v>7.45743572547261</v>
       </c>
       <c r="N3" t="n">
-        <v>88.08730757268737</v>
+        <v>87.74221647836792</v>
       </c>
       <c r="O3" t="n">
-        <v>9.38548387525584</v>
+        <v>9.367081534734707</v>
       </c>
       <c r="P3" t="n">
-        <v>295.7496035339844</v>
+        <v>295.7816929573929</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19067,28 +19141,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5169780175523883</v>
+        <v>0.5168306816292021</v>
       </c>
       <c r="J4" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K4" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1322813427938752</v>
+        <v>0.1332390311974289</v>
       </c>
       <c r="M4" t="n">
-        <v>7.234166291847595</v>
+        <v>7.203525153570717</v>
       </c>
       <c r="N4" t="n">
-        <v>81.33082681349481</v>
+        <v>80.97659231382623</v>
       </c>
       <c r="O4" t="n">
-        <v>9.018360539116564</v>
+        <v>8.99869947902619</v>
       </c>
       <c r="P4" t="n">
-        <v>294.873725726547</v>
+        <v>294.8754629834452</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19145,28 +19219,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3918542196229068</v>
+        <v>0.392840421052515</v>
       </c>
       <c r="J5" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K5" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1164011786404672</v>
+        <v>0.1178302587658642</v>
       </c>
       <c r="M5" t="n">
-        <v>5.899607768868973</v>
+        <v>5.877763060225199</v>
       </c>
       <c r="N5" t="n">
-        <v>54.07263064095188</v>
+        <v>53.84218833353793</v>
       </c>
       <c r="O5" t="n">
-        <v>7.353409456908535</v>
+        <v>7.337723647940002</v>
       </c>
       <c r="P5" t="n">
-        <v>287.9346427085615</v>
+        <v>287.9230098238363</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19227,28 +19301,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.024417923542436</v>
+        <v>1.029040051777355</v>
       </c>
       <c r="J6" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K6" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08412527728267616</v>
+        <v>0.08549915575462286</v>
       </c>
       <c r="M6" t="n">
-        <v>18.52700012837641</v>
+        <v>18.46317508164887</v>
       </c>
       <c r="N6" t="n">
-        <v>526.9067421792281</v>
+        <v>524.7172589735469</v>
       </c>
       <c r="O6" t="n">
-        <v>22.95444928939111</v>
+        <v>22.90670772881924</v>
       </c>
       <c r="P6" t="n">
-        <v>257.8891949063972</v>
+        <v>257.8344656728297</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -19290,7 +19364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G458"/>
+  <dimension ref="A1:G460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36223,6 +36297,80 @@
         </is>
       </c>
     </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-45.39117521465092,170.86416426934198</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-45.390958630269274,170.86324623899642</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-45.39093636991902,170.86226172542487</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-45.390919519550586,170.8613080826704</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-45.39094449537949,170.8603819613208</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-45.39117796050643,170.86416266509983</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-45.39096151939347,170.86324526564132</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-45.390938169558794,170.8622617292676</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-45.39091710680085,170.8613076782845</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-45.39095284562194,170.86038387413666</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G460"/>
+  <dimension ref="A1:G461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12850,6 +12850,33 @@
       <c r="G460" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>304.42</v>
+      </c>
+      <c r="C461" t="n">
+        <v>307.66</v>
+      </c>
+      <c r="D461" t="n">
+        <v>309.77</v>
+      </c>
+      <c r="E461" t="n">
+        <v>299.92</v>
+      </c>
+      <c r="F461" t="n">
+        <v>292.54</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18817,6 +18844,16 @@
       </c>
       <c r="B595" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -18985,28 +19022,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.420175610454164</v>
+        <v>1.418090214127123</v>
       </c>
       <c r="J2" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K2" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2349771917738216</v>
+        <v>0.2352269600452613</v>
       </c>
       <c r="M2" t="n">
-        <v>13.16608046115925</v>
+        <v>13.14984472570528</v>
       </c>
       <c r="N2" t="n">
-        <v>300.3485575859287</v>
+        <v>299.7357807052849</v>
       </c>
       <c r="O2" t="n">
-        <v>17.33056714553591</v>
+        <v>17.31287904149061</v>
       </c>
       <c r="P2" t="n">
-        <v>271.4941234568668</v>
+        <v>271.5190671861866</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19063,28 +19100,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5143274376738004</v>
+        <v>0.5135611776867304</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K3" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1231889717236865</v>
+        <v>0.1233393500271555</v>
       </c>
       <c r="M3" t="n">
-        <v>7.45743572547261</v>
+        <v>7.445395019012745</v>
       </c>
       <c r="N3" t="n">
-        <v>87.74221647836792</v>
+        <v>87.55763028064214</v>
       </c>
       <c r="O3" t="n">
-        <v>9.367081534734707</v>
+        <v>9.357223427953516</v>
       </c>
       <c r="P3" t="n">
-        <v>295.7816929573929</v>
+        <v>295.7907562907533</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19141,28 +19178,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5168306816292021</v>
+        <v>0.5174054533177074</v>
       </c>
       <c r="J4" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K4" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1332390311974289</v>
+        <v>0.1340058502047254</v>
       </c>
       <c r="M4" t="n">
-        <v>7.203525153570717</v>
+        <v>7.189932281848116</v>
       </c>
       <c r="N4" t="n">
-        <v>80.97659231382623</v>
+        <v>80.80402090318992</v>
       </c>
       <c r="O4" t="n">
-        <v>8.99869947902619</v>
+        <v>8.989105678719653</v>
       </c>
       <c r="P4" t="n">
-        <v>294.8754629834452</v>
+        <v>294.8686645762374</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19219,28 +19256,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.392840421052515</v>
+        <v>0.3935854484612124</v>
       </c>
       <c r="J5" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K5" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1178302587658642</v>
+        <v>0.1186774262638621</v>
       </c>
       <c r="M5" t="n">
-        <v>5.877763060225199</v>
+        <v>5.867873821185536</v>
       </c>
       <c r="N5" t="n">
-        <v>53.84218833353793</v>
+        <v>53.73096132238782</v>
       </c>
       <c r="O5" t="n">
-        <v>7.337723647940002</v>
+        <v>7.330140607272675</v>
       </c>
       <c r="P5" t="n">
-        <v>287.9230098238363</v>
+        <v>287.9141976296964</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19301,28 +19338,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.029040051777355</v>
+        <v>1.032493544818509</v>
       </c>
       <c r="J6" t="n">
+        <v>460</v>
+      </c>
+      <c r="K6" t="n">
         <v>459</v>
       </c>
-      <c r="K6" t="n">
-        <v>458</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.08549915575462286</v>
+        <v>0.08635664528361819</v>
       </c>
       <c r="M6" t="n">
-        <v>18.46317508164887</v>
+        <v>18.43559932230124</v>
       </c>
       <c r="N6" t="n">
-        <v>524.7172589735469</v>
+        <v>523.6981569027785</v>
       </c>
       <c r="O6" t="n">
-        <v>22.90670772881924</v>
+        <v>22.88445229632509</v>
       </c>
       <c r="P6" t="n">
-        <v>257.8344656728297</v>
+        <v>257.7934703485408</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -19364,7 +19401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G460"/>
+  <dimension ref="A1:G461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36371,6 +36408,43 @@
         </is>
       </c>
     </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>-45.391186614111504,170.8641576093054</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>-45.39097150000421,170.86324190314104</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>-45.39095040710925,170.86226175539815</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-45.39092363016125,170.86130877162412</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-45.39097212224534,170.8603882898944</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -12891,7 +12891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B596"/>
+  <dimension ref="A1:B597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18854,6 +18854,16 @@
       </c>
       <c r="B596" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G461"/>
+  <dimension ref="A1:G464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12877,6 +12877,87 @@
       <c r="G461" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>309.72</v>
+      </c>
+      <c r="C462" t="n">
+        <v>315.04</v>
+      </c>
+      <c r="D462" t="n">
+        <v>314.9</v>
+      </c>
+      <c r="E462" t="n">
+        <v>301.23</v>
+      </c>
+      <c r="F462" t="n">
+        <v>298.18</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>306.28</v>
+      </c>
+      <c r="C463" t="n">
+        <v>312.97</v>
+      </c>
+      <c r="D463" t="n">
+        <v>311.91</v>
+      </c>
+      <c r="E463" t="n">
+        <v>300.44</v>
+      </c>
+      <c r="F463" t="n">
+        <v>295.68</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>308.66</v>
+      </c>
+      <c r="C464" t="n">
+        <v>313.11</v>
+      </c>
+      <c r="D464" t="n">
+        <v>312.85</v>
+      </c>
+      <c r="E464" t="n">
+        <v>302.12</v>
+      </c>
+      <c r="F464" t="n">
+        <v>298.48</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12891,7 +12972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B597"/>
+  <dimension ref="A1:B600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18864,6 +18945,36 @@
       </c>
       <c r="B597" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -19032,28 +19143,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.418090214127123</v>
+        <v>1.416787397647164</v>
       </c>
       <c r="J2" t="n">
+        <v>463</v>
+      </c>
+      <c r="K2" t="n">
         <v>460</v>
       </c>
-      <c r="K2" t="n">
-        <v>457</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2352269600452613</v>
+        <v>0.2373520338978118</v>
       </c>
       <c r="M2" t="n">
-        <v>13.14984472570528</v>
+        <v>13.0743837976456</v>
       </c>
       <c r="N2" t="n">
-        <v>299.7357807052849</v>
+        <v>297.8002869659579</v>
       </c>
       <c r="O2" t="n">
-        <v>17.31287904149061</v>
+        <v>17.25689099942275</v>
       </c>
       <c r="P2" t="n">
-        <v>271.5190671861866</v>
+        <v>271.5347672917968</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19110,28 +19221,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5135611776867304</v>
+        <v>0.5193772118808112</v>
       </c>
       <c r="J3" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K3" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1233393500271555</v>
+        <v>0.1271400598231688</v>
       </c>
       <c r="M3" t="n">
-        <v>7.445395019012745</v>
+        <v>7.420579749196588</v>
       </c>
       <c r="N3" t="n">
-        <v>87.55763028064214</v>
+        <v>87.11262485192557</v>
       </c>
       <c r="O3" t="n">
-        <v>9.357223427953516</v>
+        <v>9.333414426238962</v>
       </c>
       <c r="P3" t="n">
-        <v>295.7907562907533</v>
+        <v>295.7214761909467</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19188,28 +19299,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5174054533177074</v>
+        <v>0.5236737234183201</v>
       </c>
       <c r="J4" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K4" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1340058502047254</v>
+        <v>0.1382210322552146</v>
       </c>
       <c r="M4" t="n">
-        <v>7.189932281848116</v>
+        <v>7.165363447998142</v>
       </c>
       <c r="N4" t="n">
-        <v>80.80402090318992</v>
+        <v>80.42600416533514</v>
       </c>
       <c r="O4" t="n">
-        <v>8.989105678719653</v>
+        <v>8.968054647766992</v>
       </c>
       <c r="P4" t="n">
-        <v>294.8686645762374</v>
+        <v>294.7939975517176</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19266,28 +19377,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3935854484612124</v>
+        <v>0.3975256841061166</v>
       </c>
       <c r="J5" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K5" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1186774262638621</v>
+        <v>0.1221129556599415</v>
       </c>
       <c r="M5" t="n">
-        <v>5.867873821185536</v>
+        <v>5.844738064740621</v>
       </c>
       <c r="N5" t="n">
-        <v>53.73096132238782</v>
+        <v>53.43926201335024</v>
       </c>
       <c r="O5" t="n">
-        <v>7.330140607272675</v>
+        <v>7.310216276783487</v>
       </c>
       <c r="P5" t="n">
-        <v>287.9141976296964</v>
+        <v>287.8672520839912</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19348,28 +19459,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.032493544818509</v>
+        <v>1.049210751365017</v>
       </c>
       <c r="J6" t="n">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="K6" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08635664528361819</v>
+        <v>0.08988214355930846</v>
       </c>
       <c r="M6" t="n">
-        <v>18.43559932230124</v>
+        <v>18.37556918562851</v>
       </c>
       <c r="N6" t="n">
-        <v>523.6981569027785</v>
+        <v>521.2615852285455</v>
       </c>
       <c r="O6" t="n">
-        <v>22.88445229632509</v>
+        <v>22.83115383042534</v>
       </c>
       <c r="P6" t="n">
-        <v>257.7934703485408</v>
+        <v>257.5935967605309</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -19411,7 +19522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G461"/>
+  <dimension ref="A1:G464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36455,6 +36566,117 @@
         </is>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>-45.39123071421015,170.86413184417458</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>-45.39103611132306,170.86322013534613</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>-45.39099656786924,170.86226185396328</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-45.3909353364655,170.8613107336451</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-45.391022223698855,170.86039976680766</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>-45.39120209075069,170.8641485672076</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>-45.39101798863665,170.8632262409524</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>-45.39096966325479,170.86226179651513</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-45.39092827693852,170.86130955044155</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-45.3910000156079,170.8603946795211</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>-45.39122189419097,170.86413699720404</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>-45.39101921432559,170.863225828013</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>-45.39097812156168,170.8622618145758</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-45.39094328960348,170.86131206662162</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-45.39102488866976,170.8604003772823</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G464"/>
+  <dimension ref="A1:G468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12956,6 +12956,114 @@
         <v>298.48</v>
       </c>
       <c r="G464" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>309.88</v>
+      </c>
+      <c r="C465" t="n">
+        <v>312.94</v>
+      </c>
+      <c r="D465" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="E465" t="n">
+        <v>300.41</v>
+      </c>
+      <c r="F465" t="n">
+        <v>297.22</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>312.53</v>
+      </c>
+      <c r="C466" t="n">
+        <v>312.94</v>
+      </c>
+      <c r="D466" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="E466" t="n">
+        <v>300.41</v>
+      </c>
+      <c r="F466" t="n">
+        <v>297.22</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>312.53</v>
+      </c>
+      <c r="C467" t="n">
+        <v>312.94</v>
+      </c>
+      <c r="D467" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="E467" t="n">
+        <v>301.22</v>
+      </c>
+      <c r="F467" t="n">
+        <v>299.22</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>313.89</v>
+      </c>
+      <c r="C468" t="n">
+        <v>311.31</v>
+      </c>
+      <c r="D468" t="n">
+        <v>311.53</v>
+      </c>
+      <c r="E468" t="n">
+        <v>300.03</v>
+      </c>
+      <c r="F468" t="n">
+        <v>300.03</v>
+      </c>
+      <c r="G468" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12972,7 +13080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18975,6 +19083,46 @@
       </c>
       <c r="B600" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -19143,28 +19291,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.416787397647164</v>
+        <v>1.422179435550293</v>
       </c>
       <c r="J2" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="K2" t="n">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2373520338978118</v>
+        <v>0.2419371997655653</v>
       </c>
       <c r="M2" t="n">
-        <v>13.0743837976456</v>
+        <v>12.9802253390677</v>
       </c>
       <c r="N2" t="n">
-        <v>297.8002869659579</v>
+        <v>295.3253644928637</v>
       </c>
       <c r="O2" t="n">
-        <v>17.25689099942275</v>
+        <v>17.18503315367369</v>
       </c>
       <c r="P2" t="n">
-        <v>271.5347672917968</v>
+        <v>271.4696433872147</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19221,28 +19369,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5193772118808112</v>
+        <v>0.5246904167516372</v>
       </c>
       <c r="J3" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="K3" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1271400598231688</v>
+        <v>0.1313243585677205</v>
       </c>
       <c r="M3" t="n">
-        <v>7.420579749196588</v>
+        <v>7.378106590669668</v>
       </c>
       <c r="N3" t="n">
-        <v>87.11262485192557</v>
+        <v>86.44580910500092</v>
       </c>
       <c r="O3" t="n">
-        <v>9.333414426238962</v>
+        <v>9.297623841874918</v>
       </c>
       <c r="P3" t="n">
-        <v>295.7214761909467</v>
+        <v>295.6580512513146</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19299,28 +19447,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5236737234183201</v>
+        <v>0.5311994072752165</v>
       </c>
       <c r="J4" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="K4" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1382210322552146</v>
+        <v>0.1435862350862849</v>
       </c>
       <c r="M4" t="n">
-        <v>7.165363447998142</v>
+        <v>7.13067390359975</v>
       </c>
       <c r="N4" t="n">
-        <v>80.42600416533514</v>
+        <v>79.89347627347404</v>
       </c>
       <c r="O4" t="n">
-        <v>8.968054647766992</v>
+        <v>8.9383150690426</v>
       </c>
       <c r="P4" t="n">
-        <v>294.7939975517176</v>
+        <v>294.7041586986629</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19377,28 +19525,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3975256841061166</v>
+        <v>0.4012125050159432</v>
       </c>
       <c r="J5" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="K5" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1221129556599415</v>
+        <v>0.1259700483688665</v>
       </c>
       <c r="M5" t="n">
-        <v>5.844738064740621</v>
+        <v>5.808508834553319</v>
       </c>
       <c r="N5" t="n">
-        <v>53.43926201335024</v>
+        <v>53.01921151110995</v>
       </c>
       <c r="O5" t="n">
-        <v>7.310216276783487</v>
+        <v>7.281429221733186</v>
       </c>
       <c r="P5" t="n">
-        <v>287.8672520839912</v>
+        <v>287.8232344119707</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19459,28 +19607,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.049210751365017</v>
+        <v>1.072255159676866</v>
       </c>
       <c r="J6" t="n">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="K6" t="n">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08988214355930846</v>
+        <v>0.09478539696903732</v>
       </c>
       <c r="M6" t="n">
-        <v>18.37556918562851</v>
+        <v>18.29938593343135</v>
       </c>
       <c r="N6" t="n">
-        <v>521.2615852285455</v>
+        <v>518.1956152631027</v>
       </c>
       <c r="O6" t="n">
-        <v>22.83115383042534</v>
+        <v>22.76391036845609</v>
       </c>
       <c r="P6" t="n">
-        <v>257.5935967605309</v>
+        <v>257.3174485724105</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -19522,7 +19670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G464"/>
+  <dimension ref="A1:G468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36677,6 +36825,154 @@
         </is>
       </c>
     </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>-45.391232045533776,170.86413106635868</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>-45.391017725989016,170.8632263294394</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>-45.390983520480965,170.86226182610386</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-45.39092800885521,170.86130950550978</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-45.391013695791955,170.86039781328918</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>-45.39125409558042,170.86411818377724</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>-45.391017725989016,170.8632263294394</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>-45.390983520480965,170.86226182610386</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-45.39092800885521,170.86130950550978</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-45.391013695791955,170.86039781328918</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>-45.39125409558042,170.86411818377724</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>-45.391017725989016,170.8632263294394</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>-45.390983520480965,170.86226182610386</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-45.39093524710439,170.86131071866785</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>-45.39103146226462,170.86040188311995</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>-45.3912654118301,170.8641115723352</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>-45.3910034554675,170.86323113723276</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>-45.39096624393923,170.862261789214</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-45.39092461313336,170.86130893637397</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-45.39103865768601,170.86040353140206</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G468"/>
+  <dimension ref="A1:G474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13061,9 +13061,171 @@
         <v>300.03</v>
       </c>
       <c r="F468" t="n">
-        <v>300.03</v>
+        <v>296.28</v>
       </c>
       <c r="G468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>313.89</v>
+      </c>
+      <c r="C469" t="n">
+        <v>310.35</v>
+      </c>
+      <c r="D469" t="n">
+        <v>310.16</v>
+      </c>
+      <c r="E469" t="n">
+        <v>299.17</v>
+      </c>
+      <c r="F469" t="n">
+        <v>292.64</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>314.9</v>
+      </c>
+      <c r="C470" t="n">
+        <v>309.2</v>
+      </c>
+      <c r="D470" t="n">
+        <v>310.13</v>
+      </c>
+      <c r="E470" t="n">
+        <v>296.62</v>
+      </c>
+      <c r="F470" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>314.9</v>
+      </c>
+      <c r="C471" t="n">
+        <v>308.16</v>
+      </c>
+      <c r="D471" t="n">
+        <v>308.4</v>
+      </c>
+      <c r="E471" t="n">
+        <v>295.73</v>
+      </c>
+      <c r="F471" t="n">
+        <v>280.83</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>314.48</v>
+      </c>
+      <c r="C472" t="n">
+        <v>307.87</v>
+      </c>
+      <c r="D472" t="n">
+        <v>308.24</v>
+      </c>
+      <c r="E472" t="n">
+        <v>293.05</v>
+      </c>
+      <c r="F472" t="n">
+        <v>279.54</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>314.48</v>
+      </c>
+      <c r="C473" t="n">
+        <v>308.55</v>
+      </c>
+      <c r="D473" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="E473" t="n">
+        <v>294.56</v>
+      </c>
+      <c r="F473" t="n">
+        <v>272.71</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="C474" t="n">
+        <v>308.55</v>
+      </c>
+      <c r="D474" t="n">
+        <v>308.9</v>
+      </c>
+      <c r="E474" t="n">
+        <v>297.87</v>
+      </c>
+      <c r="F474" t="n">
+        <v>272.71</v>
+      </c>
+      <c r="G474" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13080,7 +13242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B604"/>
+  <dimension ref="A1:B610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19123,6 +19285,66 @@
       </c>
       <c r="B604" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -19291,28 +19513,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.422179435550293</v>
+        <v>1.446109802827879</v>
       </c>
       <c r="J2" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K2" t="n">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2419371997655653</v>
+        <v>0.251721870653803</v>
       </c>
       <c r="M2" t="n">
-        <v>12.9802253390677</v>
+        <v>12.89480689206991</v>
       </c>
       <c r="N2" t="n">
-        <v>295.3253644928637</v>
+        <v>293.5900282470316</v>
       </c>
       <c r="O2" t="n">
-        <v>17.18503315367369</v>
+        <v>17.13446900977768</v>
       </c>
       <c r="P2" t="n">
-        <v>271.4696433872147</v>
+        <v>271.1793444027792</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19369,28 +19591,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5246904167516372</v>
+        <v>0.5223897002063684</v>
       </c>
       <c r="J3" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K3" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1313243585677205</v>
+        <v>0.1332791040563295</v>
       </c>
       <c r="M3" t="n">
-        <v>7.378106590669668</v>
+        <v>7.300424929908989</v>
       </c>
       <c r="N3" t="n">
-        <v>86.44580910500092</v>
+        <v>85.3674633046877</v>
       </c>
       <c r="O3" t="n">
-        <v>9.297623841874918</v>
+        <v>9.239451461244206</v>
       </c>
       <c r="P3" t="n">
-        <v>295.6580512513146</v>
+        <v>295.6856598102506</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19447,28 +19669,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5311994072752165</v>
+        <v>0.5317977540000937</v>
       </c>
       <c r="J4" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K4" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1435862350862849</v>
+        <v>0.1470860791929114</v>
       </c>
       <c r="M4" t="n">
-        <v>7.13067390359975</v>
+        <v>7.047365691012068</v>
       </c>
       <c r="N4" t="n">
-        <v>79.89347627347404</v>
+        <v>78.8882990322283</v>
       </c>
       <c r="O4" t="n">
-        <v>8.9383150690426</v>
+        <v>8.881908524198407</v>
       </c>
       <c r="P4" t="n">
-        <v>294.7041586986629</v>
+        <v>294.6970065811362</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19525,28 +19747,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4012125050159432</v>
+        <v>0.3950764206798019</v>
       </c>
       <c r="J5" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K5" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1259700483688665</v>
+        <v>0.1251905579539706</v>
       </c>
       <c r="M5" t="n">
-        <v>5.808508834553319</v>
+        <v>5.773440132210639</v>
       </c>
       <c r="N5" t="n">
-        <v>53.01921151110995</v>
+        <v>52.46746370571828</v>
       </c>
       <c r="O5" t="n">
-        <v>7.281429221733186</v>
+        <v>7.243442807513446</v>
       </c>
       <c r="P5" t="n">
-        <v>287.8232344119707</v>
+        <v>287.8968391270013</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19607,28 +19829,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.072255159676866</v>
+        <v>1.056937921145958</v>
       </c>
       <c r="J6" t="n">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="K6" t="n">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09478539696903732</v>
+        <v>0.09442566097346328</v>
       </c>
       <c r="M6" t="n">
-        <v>18.29938593343135</v>
+        <v>18.17139422739195</v>
       </c>
       <c r="N6" t="n">
-        <v>518.1956152631027</v>
+        <v>512.3821447871173</v>
       </c>
       <c r="O6" t="n">
-        <v>22.76391036845609</v>
+        <v>22.63585970947685</v>
       </c>
       <c r="P6" t="n">
-        <v>257.3174485724105</v>
+        <v>257.5019442484852</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -19670,7 +19892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G468"/>
+  <dimension ref="A1:G474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36964,10 +37186,232 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>-45.39103865768601,170.86040353140206</t>
+          <t>-45.39100534554974,170.86039590046954</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>-45.3912654118301,170.8641115723352</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>-45.390995050743044,170.86323396881534</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>-45.39095391640681,170.86226176289142</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-45.390916928078646,170.86130764833004</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>-45.390973010569,170.8603884933856</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>-45.39127381580936,170.8641066623655</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>-45.39098498258342,170.86323736081417</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>-45.39095364646084,170.86226176231503</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-45.39089414099771,170.86130382913177</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-45.39091180506833,170.8603744728552</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>-45.39127381580936,170.8641066623655</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>-45.39097587746502,170.86324042835986</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>-45.390938079576806,170.86226172907547</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-45.39088618785962,170.86130249615732</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-45.39086809954281,170.86036446111476</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>-45.391270321085344,170.86410870413522</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>-45.39097333853775,170.86324128373298</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>-45.39093663986498,170.86226172600126</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-45.39086223908413,170.8612984822588</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>-45.39085664016706,170.86036183608758</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>-45.391270321085344,170.86410870413522</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>-45.39097929188443,170.86323927803033</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>-45.390942578676245,170.8622617386823</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-45.390875732610645,170.86130074382066</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-45.39079596765725,170.8603479377043</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>-45.39147076840032,170.8639915936371</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>-45.39097929188443,170.86323927803033</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>-45.390942578676245,170.8622617386823</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-45.39090531113544,170.86130570128742</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-45.39079596765725,170.8603479377043</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0488/nzd0488.xlsx
+++ b/data/nzd0488/nzd0488.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G474"/>
+  <dimension ref="A1:G475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13193,7 +13193,7 @@
         <v>308.9</v>
       </c>
       <c r="E473" t="n">
-        <v>294.56</v>
+        <v>293.05</v>
       </c>
       <c r="F473" t="n">
         <v>272.71</v>
@@ -13220,7 +13220,7 @@
         <v>308.9</v>
       </c>
       <c r="E474" t="n">
-        <v>297.87</v>
+        <v>293.05</v>
       </c>
       <c r="F474" t="n">
         <v>272.71</v>
@@ -13228,6 +13228,33 @@
       <c r="G474" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="C475" t="n">
+        <v>301.76</v>
+      </c>
+      <c r="D475" t="n">
+        <v>307.15</v>
+      </c>
+      <c r="E475" t="n">
+        <v>291.53</v>
+      </c>
+      <c r="F475" t="n">
+        <v>263.39</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B610"/>
+  <dimension ref="A1:B611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19345,6 +19372,16 @@
       </c>
       <c r="B610" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -19513,28 +19550,28 @@
         <v>0.0527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.446109802827879</v>
+        <v>1.459788097551448</v>
       </c>
       <c r="J2" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K2" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L2" t="n">
-        <v>0.251721870653803</v>
+        <v>0.2547809299572188</v>
       </c>
       <c r="M2" t="n">
-        <v>12.89480689206991</v>
+        <v>12.91299005942706</v>
       </c>
       <c r="N2" t="n">
-        <v>293.5900282470316</v>
+        <v>295.014888056528</v>
       </c>
       <c r="O2" t="n">
-        <v>17.13446900977768</v>
+        <v>17.17599743993134</v>
       </c>
       <c r="P2" t="n">
-        <v>271.1793444027792</v>
+        <v>271.0129547336263</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19591,28 +19628,28 @@
         <v>0.0465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5223897002063684</v>
+        <v>0.5189671448828749</v>
       </c>
       <c r="J3" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K3" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1332791040563295</v>
+        <v>0.1320815791241371</v>
       </c>
       <c r="M3" t="n">
-        <v>7.300424929908989</v>
+        <v>7.304106007374088</v>
       </c>
       <c r="N3" t="n">
-        <v>85.3674633046877</v>
+        <v>85.31892210540958</v>
       </c>
       <c r="O3" t="n">
-        <v>9.239451461244206</v>
+        <v>9.236824243505426</v>
       </c>
       <c r="P3" t="n">
-        <v>295.6856598102506</v>
+        <v>295.7268384461051</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19669,28 +19706,28 @@
         <v>0.0431</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5317977540000937</v>
+        <v>0.5310230782486586</v>
       </c>
       <c r="J4" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K4" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1470860791929114</v>
+        <v>0.1472469994416379</v>
       </c>
       <c r="M4" t="n">
-        <v>7.047365691012068</v>
+        <v>7.037154605288613</v>
       </c>
       <c r="N4" t="n">
-        <v>78.8882990322283</v>
+        <v>78.72860801261699</v>
       </c>
       <c r="O4" t="n">
-        <v>8.881908524198407</v>
+        <v>8.872914290841369</v>
       </c>
       <c r="P4" t="n">
-        <v>294.6970065811362</v>
+        <v>294.7063271289896</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19747,28 +19784,28 @@
         <v>0.0542</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3950764206798019</v>
+        <v>0.3893585988231256</v>
       </c>
       <c r="J5" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K5" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1251905579539706</v>
+        <v>0.1221031313811202</v>
       </c>
       <c r="M5" t="n">
-        <v>5.773440132210639</v>
+        <v>5.794587508231648</v>
       </c>
       <c r="N5" t="n">
-        <v>52.46746370571828</v>
+        <v>52.54667220970775</v>
       </c>
       <c r="O5" t="n">
-        <v>7.243442807513446</v>
+        <v>7.248908346068927</v>
       </c>
       <c r="P5" t="n">
-        <v>287.8968391270013</v>
+        <v>287.9655643285475</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -19829,28 +19866,28 @@
         <v>0.0601</v>
       </c>
       <c r="I6" t="n">
-        <v>1.056937921145958</v>
+        <v>1.047200997662801</v>
       </c>
       <c r="J6" t="n">
+        <v>474</v>
+      </c>
+      <c r="K6" t="n">
         <v>473</v>
       </c>
-      <c r="K6" t="n">
-        <v>472</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.09442566097346328</v>
+        <v>0.09304261584279261</v>
       </c>
       <c r="M6" t="n">
-        <v>18.17139422739195</v>
+        <v>18.19172737814321</v>
       </c>
       <c r="N6" t="n">
-        <v>512.3821447871173</v>
+        <v>512.3551970388645</v>
       </c>
       <c r="O6" t="n">
-        <v>22.63585970947685</v>
+        <v>22.63526445701186</v>
       </c>
       <c r="P6" t="n">
-        <v>257.5019442484852</v>
+        <v>257.6195098534452</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -19892,7 +19929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G474"/>
+  <dimension ref="A1:G475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37366,7 +37403,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>-45.390875732610645,170.86130074382066</t>
+          <t>-45.39086223908413,170.8612984822588</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -37403,7 +37440,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>-45.39090531113544,170.86130570128742</t>
+          <t>-45.39086223908413,170.8612984822588</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -37414,6 +37451,43 @@
       <c r="G474" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>-45.39149165352127,170.8639793915396</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>-45.390919845964696,170.8632593055412</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>-45.39092683182819,170.86226170505836</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-45.39084865619646,170.8612962057207</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>-45.39071317588408,170.86032897245832</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
